--- a/satisfaction_surveys/037_share_your_change_experiences--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/037_share_your_change_experiences--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Status1</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Status2</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>status3</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Status3</t>
+          <t>Status 3</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>status4</t>
+          <t>status_4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Status4</t>
+          <t>Status 4</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>status5</t>
+          <t>status_5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Status5</t>
+          <t>Status 5</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>status6</t>
+          <t>status_6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Status6</t>
+          <t>Status 6</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>status7</t>
+          <t>status_7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Status7</t>
+          <t>Status 7</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>status8</t>
+          <t>status_8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Status8</t>
+          <t>Status 8</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>status9</t>
+          <t>status_9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Status9</t>
+          <t>Status 9</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>status10</t>
+          <t>status_10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Status10</t>
+          <t>Status 10</t>
         </is>
       </c>
     </row>
